--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_126_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_126_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2663</v>
+        <v>3.9796</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0794</v>
+        <v>2.7255</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1869</v>
+        <v>1.2541</v>
       </c>
       <c r="G2" t="n">
         <v>1.2441</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5403</v>
+        <v>0.2537</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5272</v>
+        <v>0.1733</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0132</v>
+        <v>0.0804</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2487</v>
+        <v>1.794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4158</v>
+        <v>0.0619</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8329</v>
+        <v>1.7321</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1635</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.322</v>
+        <v>-0.1327</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0395</v>
+        <v>-0.3143</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2825</v>
+        <v>0.1817</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0066</v>
+        <v>1.0704</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7792</v>
+        <v>0.0617</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7859</v>
+        <v>1.0087</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1369</v>
+        <v>-0.2819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3409</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.204</v>
+        <v>0.4182</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4745</v>
+        <v>1.2586</v>
       </c>
       <c r="K4" t="n">
-        <v>0.091</v>
+        <v>0.0476</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5655</v>
+        <v>1.211</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6114000000000001</v>
+        <v>-1.5405</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2499</v>
+        <v>-0.7477</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3615</v>
+        <v>-0.7929</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2473</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5503</v>
+        <v>0.5996</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0148</v>
+        <v>0.1379</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5355</v>
+        <v>0.4617</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5567</v>
+        <v>0.5371</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.625</v>
+        <v>-2.3539</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1817</v>
+        <v>2.891</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0165</v>
+        <v>-1.8019</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4309</v>
+        <v>-1.6111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5856</v>
+        <v>-0.1908</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8949</v>
+        <v>-1.9414</v>
       </c>
       <c r="K5" t="n">
-        <v>0.306</v>
+        <v>-1.7036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5889</v>
+        <v>-0.2378</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1217</v>
+        <v>0.1396</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1249</v>
+        <v>0.0926</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0033</v>
+        <v>0.047</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0917</v>
+        <v>-0.0707</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2636</v>
+        <v>-0.4125</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.3418</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.397</v>
+        <v>0.4443</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4101</v>
+        <v>0.8986</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8071</v>
+        <v>-0.4544</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2819</v>
+        <v>-2.3028</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.4525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4182</v>
+        <v>-1.8503</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2586</v>
+        <v>-0.5551</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0476</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.211</v>
+        <v>-0.6391</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5405</v>
+        <v>-1.7477</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7477</v>
+        <v>-0.5365</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7929</v>
+        <v>-1.2112</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0738</v>
+        <v>0.747</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3339</v>
+        <v>0.3815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2601</v>
+        <v>0.3655</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3263</v>
+        <v>0.2221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7806999999999999</v>
+        <v>-2.5302</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4544</v>
+        <v>2.7523</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3028</v>
+        <v>0.1369</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4525</v>
+        <v>0.3409</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8503</v>
+        <v>-0.204</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5551</v>
+        <v>-0.4745</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6391</v>
+        <v>-0.5655</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7477</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5365</v>
+        <v>0.2499</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2112</v>
+        <v>0.3615</v>
       </c>
       <c r="P7" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>3.2473</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6291</v>
+        <v>0.7657</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>0.2638</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3655</v>
+        <v>0.5019</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5142</v>
+        <v>0.1363</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1363</v>
+        <v>-0.7429</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6222</v>
+        <v>0.8792</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8019</v>
+        <v>1.0165</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6111</v>
+        <v>0.4309</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1908</v>
+        <v>0.5856</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9414</v>
+        <v>0.8949</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7036</v>
+        <v>0.306</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2378</v>
+        <v>0.5889</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1396</v>
+        <v>0.1217</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0926</v>
+        <v>0.1249</v>
       </c>
       <c r="O8" t="n">
-        <v>0.047</v>
+        <v>-0.0033</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5515</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.122</v>
+        <v>0.6713</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1949</v>
+        <v>0.1456</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.5256</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0848</v>
+        <v>-0.8428</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9828</v>
+        <v>-3.1441</v>
       </c>
       <c r="F9" t="n">
-        <v>1.898</v>
+        <v>2.3013</v>
       </c>
       <c r="G9" t="n">
         <v>0.6607</v>
@@ -1156,13 +1156,13 @@
         <v>3.0154</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.297</v>
+        <v>-0.0549</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2197</v>
+        <v>-0.3809</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.326</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3737</v>
+        <v>-1.4327</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0401</v>
+        <v>-2.7295</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6665</v>
+        <v>1.2968</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2119</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5162</v>
+        <v>0.4571</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4832</v>
+        <v>-0.1727</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9994</v>
+        <v>0.6297</v>
       </c>
       <c r="V10" t="n">
         <v>0.9304</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7551</v>
+        <v>-2.461</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6505</v>
+        <v>-4.222</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8954</v>
+        <v>1.761</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7323</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7187</v>
+        <v>-0.4246</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2696</v>
+        <v>-0.841</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.4165</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.073800000000001</v>
+        <v>3.447300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.3481</v>
+        <v>-11.9749</v>
       </c>
       <c r="F12" t="n">
-        <v>15.4222</v>
+        <v>15.4221</v>
       </c>
       <c r="G12" t="n">
         <v>-8.4361</v>
@@ -1369,7 +1369,7 @@
         <v>-7.1625</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8353999999999999</v>
+        <v>0.8353999999999995</v>
       </c>
       <c r="M12" t="n">
         <v>-2.1088</v>
@@ -1378,10 +1378,10 @@
         <v>-2.3273</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2184999999999997</v>
+        <v>0.2184999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>6.9587</v>
+        <v>6.958699999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.5976</v>
@@ -1390,10 +1390,10 @@
         <v>18.5563</v>
       </c>
       <c r="S12" t="n">
-        <v>2.438099999999999</v>
+        <v>2.811500000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3926</v>
+        <v>-1.0193</v>
       </c>
       <c r="U12" t="n">
         <v>3.8308</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8496</v>
+        <v>2.4894</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.348</v>
+        <v>0.1238</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1976</v>
+        <v>2.3656</v>
       </c>
       <c r="G13" t="n">
         <v>2.4648</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1461</v>
+        <v>-0.5063</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1949</v>
+        <v>-0.7231</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0488</v>
+        <v>0.2168</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3247</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4509</v>
+        <v>1.872</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0102</v>
+        <v>0.3641</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4407</v>
+        <v>1.5079</v>
       </c>
       <c r="G14" t="n">
         <v>3.7493</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9067</v>
+        <v>-0.4856</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3093</v>
+        <v>-0.242</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2789</v>
+        <v>1.2542</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.495</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7738</v>
+        <v>1.3207</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1775</v>
+        <v>3.494</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6855</v>
+        <v>0.9712</v>
       </c>
       <c r="I15" t="n">
-        <v>0.492</v>
+        <v>2.5228</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7634</v>
+        <v>3.0507</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9474</v>
+        <v>0.5749</v>
       </c>
       <c r="L15" t="n">
-        <v>0.184</v>
+        <v>2.4759</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9409</v>
+        <v>0.4433</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6329</v>
+        <v>0.3963</v>
       </c>
       <c r="O15" t="n">
-        <v>0.308</v>
+        <v>0.047</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.2473</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8847</v>
+        <v>-0.2399</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2991</v>
+        <v>-0.7978</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5856</v>
+        <v>0.5579</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5384</v>
+        <v>0.4189</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4552</v>
+        <v>0.4627</v>
       </c>
       <c r="G16" t="n">
-        <v>3.494</v>
+        <v>-0.2193</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9712</v>
+        <v>0.2124</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5228</v>
+        <v>-0.4317</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0507</v>
+        <v>-0.3589</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5749</v>
+        <v>-0.1947</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4759</v>
+        <v>-0.1642</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4433</v>
+        <v>0.1396</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3963</v>
+        <v>0.4071</v>
       </c>
       <c r="O16" t="n">
-        <v>0.047</v>
+        <v>-0.2676</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5772</v>
+        <v>-1.0409</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2696</v>
+        <v>-0.4362</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6923</v>
+        <v>-0.6047</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7155</v>
+        <v>0.867</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3198</v>
+        <v>-0.2018</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0353</v>
+        <v>1.0689</v>
       </c>
       <c r="G17" t="n">
         <v>0.7756999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2921</v>
+        <v>-0.1406</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0813</v>
+        <v>0.1149</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4776</v>
+        <v>0.0825</v>
       </c>
       <c r="E18" t="n">
-        <v>0.183</v>
+        <v>-2.076</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2946</v>
+        <v>2.1585</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2193</v>
+        <v>2.5503</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2124</v>
+        <v>0.3386</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4317</v>
+        <v>2.2117</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3589</v>
+        <v>0.8132</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1947</v>
+        <v>-0.7191</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1642</v>
+        <v>1.5324</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1396</v>
+        <v>1.7371</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4071</v>
+        <v>1.0578</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2676</v>
+        <v>0.6793</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4449</v>
+        <v>-0.2359</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6721</v>
+        <v>-0.5698</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.3339</v>
       </c>
       <c r="V18" t="n">
-        <v>1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3184</v>
+        <v>-0.2312</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8401</v>
+        <v>0.4588</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1585</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5503</v>
+        <v>1.1324</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3386</v>
+        <v>0.52</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2117</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8132</v>
+        <v>2.0115</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7191</v>
+        <v>0.1344</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5324</v>
+        <v>1.8771</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7371</v>
+        <v>-0.8791</v>
       </c>
       <c r="N19" t="n">
-        <v>1.0578</v>
+        <v>0.3856</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6793</v>
+        <v>-1.2647</v>
       </c>
       <c r="P19" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0</v>
+        <v>0.0127</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3339</v>
+        <v>-0.393</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3339</v>
+        <v>0.4057</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4468</v>
+        <v>-0.2781</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0173</v>
+        <v>0.2186</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4295</v>
+        <v>-0.4967</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1621</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.3479</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1432</v>
+        <v>-0.2104</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.576</v>
+        <v>-0.7776</v>
       </c>
       <c r="E21" t="n">
         <v>-0.905</v>
       </c>
       <c r="F21" t="n">
-        <v>0.329</v>
+        <v>0.1274</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0365</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0756</v>
+        <v>-0.2772</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2978</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6187</v>
+        <v>-1.6693</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1049</v>
+        <v>-3.2079</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7236</v>
+        <v>1.5386</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1324</v>
+        <v>1.1775</v>
       </c>
       <c r="H22" t="n">
-        <v>0.52</v>
+        <v>0.6855</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.492</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0115</v>
+        <v>-0.7634</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1344</v>
+        <v>-0.9474</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8771</v>
+        <v>0.184</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8791</v>
+        <v>1.9409</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3856</v>
+        <v>1.6329</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2647</v>
+        <v>0.308</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3747</v>
+        <v>0.9366</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3721</v>
+        <v>0.3504</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.440099999999999</v>
+        <v>-7.5643</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.2567</v>
+        <v>-10.549</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8166</v>
+        <v>2.9847</v>
       </c>
       <c r="G23" t="n">
         <v>-6.4901</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9889</v>
+        <v>-0.1131</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1949</v>
+        <v>-0.4872</v>
       </c>
       <c r="U23" t="n">
-        <v>0.206</v>
+        <v>0.3741</v>
       </c>
       <c r="V23" t="n">
         <v>2.2862</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.073899999999998</v>
+        <v>-3.0738</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.4222</v>
+        <v>-15.4221</v>
       </c>
       <c r="F24" t="n">
-        <v>12.3482</v>
+        <v>12.3483</v>
       </c>
       <c r="G24" t="n">
-        <v>8.436</v>
+        <v>8.436000000000002</v>
       </c>
       <c r="H24" t="n">
         <v>9.49</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.053899999999999</v>
+        <v>-1.0539</v>
       </c>
       <c r="J24" t="n">
         <v>2.108699999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3274</v>
+        <v>2.327400000000001</v>
       </c>
       <c r="L24" t="n">
         <v>-0.2183999999999999</v>
@@ -2311,7 +2311,7 @@
         <v>6.327500000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>7.1628</v>
+        <v>7.162800000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-0.8353999999999999</v>
@@ -2329,13 +2329,13 @@
         <v>-2.4381</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.8308</v>
+        <v>-3.8309</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3926</v>
+        <v>1.3928</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1133</v>
+        <v>-2.113300000000001</v>
       </c>
       <c r="W24" t="n">
         <v>4.856</v>
